--- a/inversiones.xlsx
+++ b/inversiones.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marag\OneDrive\Escritorio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marag\OneDrive\Documentos\GitHub\inversiones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9F03EF7-C133-47DF-A90A-11D90C87A409}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB0799A5-AE6D-439D-AEAD-F1D3C252CAB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -890,31 +890,37 @@
       <c r="A6" s="4">
         <v>3</v>
       </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="6"/>
+      <c r="B6" s="5">
+        <v>46169</v>
+      </c>
+      <c r="C6" s="6">
+        <v>103</v>
+      </c>
       <c r="D6" s="7">
         <v>3</v>
       </c>
       <c r="E6" s="8">
         <f t="shared" si="0"/>
-        <v>-3</v>
-      </c>
-      <c r="F6" s="6"/>
+        <v>100</v>
+      </c>
+      <c r="F6" s="6">
+        <v>319</v>
+      </c>
       <c r="G6" s="9">
         <f>SUM($C$4:C6)</f>
-        <v>203</v>
-      </c>
-      <c r="H6" s="9" t="str">
+        <v>306</v>
+      </c>
+      <c r="H6" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I6" s="10" t="str">
+        <v>13</v>
+      </c>
+      <c r="I6" s="10">
         <f t="shared" si="2"/>
-        <v/>
+        <v>4.2483660130719025E-2</v>
       </c>
       <c r="J6" s="9">
         <f>AVERAGE($E$4:E6)</f>
-        <v>64.666666666666671</v>
+        <v>99</v>
       </c>
       <c r="K6" s="11"/>
     </row>
@@ -934,7 +940,7 @@
       <c r="F7" s="6"/>
       <c r="G7" s="14">
         <f>SUM($C$4:C7)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H7" s="14" t="str">
         <f t="shared" si="1"/>
@@ -946,7 +952,7 @@
       </c>
       <c r="J7" s="14">
         <f>AVERAGE($E$4:E7)</f>
-        <v>47.75</v>
+        <v>73.5</v>
       </c>
       <c r="K7" s="11"/>
     </row>
@@ -966,7 +972,7 @@
       <c r="F8" s="6"/>
       <c r="G8" s="9">
         <f>SUM($C$4:C8)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H8" s="9" t="str">
         <f t="shared" si="1"/>
@@ -978,7 +984,7 @@
       </c>
       <c r="J8" s="9">
         <f>AVERAGE($E$4:E8)</f>
-        <v>37.6</v>
+        <v>58.2</v>
       </c>
       <c r="K8" s="11"/>
     </row>
@@ -998,7 +1004,7 @@
       <c r="F9" s="6"/>
       <c r="G9" s="14">
         <f>SUM($C$4:C9)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H9" s="14" t="str">
         <f t="shared" si="1"/>
@@ -1010,7 +1016,7 @@
       </c>
       <c r="J9" s="14">
         <f>AVERAGE($E$4:E9)</f>
-        <v>30.833333333333332</v>
+        <v>48</v>
       </c>
       <c r="K9" s="11"/>
     </row>
@@ -1030,7 +1036,7 @@
       <c r="F10" s="6"/>
       <c r="G10" s="9">
         <f>SUM($C$4:C10)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H10" s="9" t="str">
         <f t="shared" si="1"/>
@@ -1042,7 +1048,7 @@
       </c>
       <c r="J10" s="9">
         <f>AVERAGE($E$4:E10)</f>
-        <v>26</v>
+        <v>40.714285714285715</v>
       </c>
       <c r="K10" s="11"/>
     </row>
@@ -1062,7 +1068,7 @@
       <c r="F11" s="6"/>
       <c r="G11" s="14">
         <f>SUM($C$4:C11)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H11" s="14" t="str">
         <f t="shared" si="1"/>
@@ -1074,7 +1080,7 @@
       </c>
       <c r="J11" s="14">
         <f>AVERAGE($E$4:E11)</f>
-        <v>22.375</v>
+        <v>35.25</v>
       </c>
       <c r="K11" s="11"/>
     </row>
@@ -1094,7 +1100,7 @@
       <c r="F12" s="6"/>
       <c r="G12" s="9">
         <f>SUM($C$4:C12)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H12" s="9" t="str">
         <f t="shared" si="1"/>
@@ -1106,7 +1112,7 @@
       </c>
       <c r="J12" s="9">
         <f>AVERAGE($E$4:E12)</f>
-        <v>19.555555555555557</v>
+        <v>31</v>
       </c>
       <c r="K12" s="11"/>
     </row>
@@ -1126,7 +1132,7 @@
       <c r="F13" s="6"/>
       <c r="G13" s="14">
         <f>SUM($C$4:C13)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H13" s="14" t="str">
         <f t="shared" si="1"/>
@@ -1138,7 +1144,7 @@
       </c>
       <c r="J13" s="14">
         <f>AVERAGE($E$4:E13)</f>
-        <v>17.3</v>
+        <v>27.6</v>
       </c>
       <c r="K13" s="11"/>
     </row>
@@ -1158,7 +1164,7 @@
       <c r="F14" s="6"/>
       <c r="G14" s="9">
         <f>SUM($C$4:C14)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H14" s="9" t="str">
         <f t="shared" si="1"/>
@@ -1170,7 +1176,7 @@
       </c>
       <c r="J14" s="9">
         <f>AVERAGE($E$4:E14)</f>
-        <v>15.454545454545455</v>
+        <v>24.818181818181817</v>
       </c>
       <c r="K14" s="11"/>
     </row>
@@ -1190,7 +1196,7 @@
       <c r="F15" s="6"/>
       <c r="G15" s="14">
         <f>SUM($C$4:C15)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H15" s="14" t="str">
         <f t="shared" si="1"/>
@@ -1202,7 +1208,7 @@
       </c>
       <c r="J15" s="14">
         <f>AVERAGE($E$4:E15)</f>
-        <v>13.916666666666666</v>
+        <v>22.5</v>
       </c>
       <c r="K15" s="11"/>
     </row>
@@ -1222,7 +1228,7 @@
       <c r="F16" s="6"/>
       <c r="G16" s="9">
         <f>SUM($C$4:C16)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H16" s="9" t="str">
         <f t="shared" si="1"/>
@@ -1234,7 +1240,7 @@
       </c>
       <c r="J16" s="9">
         <f>AVERAGE($E$4:E16)</f>
-        <v>12.615384615384615</v>
+        <v>20.53846153846154</v>
       </c>
       <c r="K16" s="11"/>
     </row>
@@ -1254,7 +1260,7 @@
       <c r="F17" s="6"/>
       <c r="G17" s="14">
         <f>SUM($C$4:C17)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H17" s="14" t="str">
         <f t="shared" si="1"/>
@@ -1266,7 +1272,7 @@
       </c>
       <c r="J17" s="14">
         <f>AVERAGE($E$4:E17)</f>
-        <v>11.5</v>
+        <v>18.857142857142858</v>
       </c>
       <c r="K17" s="11"/>
     </row>
@@ -1286,7 +1292,7 @@
       <c r="F18" s="6"/>
       <c r="G18" s="9">
         <f>SUM($C$4:C18)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H18" s="9" t="str">
         <f t="shared" si="1"/>
@@ -1298,7 +1304,7 @@
       </c>
       <c r="J18" s="9">
         <f>AVERAGE($E$4:E18)</f>
-        <v>10.533333333333333</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="K18" s="11"/>
     </row>
@@ -1318,7 +1324,7 @@
       <c r="F19" s="6"/>
       <c r="G19" s="14">
         <f>SUM($C$4:C19)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H19" s="14" t="str">
         <f t="shared" si="1"/>
@@ -1330,7 +1336,7 @@
       </c>
       <c r="J19" s="14">
         <f>AVERAGE($E$4:E19)</f>
-        <v>9.6875</v>
+        <v>16.125</v>
       </c>
       <c r="K19" s="11"/>
     </row>
@@ -1350,7 +1356,7 @@
       <c r="F20" s="6"/>
       <c r="G20" s="9">
         <f>SUM($C$4:C20)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H20" s="9" t="str">
         <f t="shared" si="1"/>
@@ -1362,7 +1368,7 @@
       </c>
       <c r="J20" s="9">
         <f>AVERAGE($E$4:E20)</f>
-        <v>8.9411764705882355</v>
+        <v>15</v>
       </c>
       <c r="K20" s="11"/>
     </row>
@@ -1382,7 +1388,7 @@
       <c r="F21" s="6"/>
       <c r="G21" s="14">
         <f>SUM($C$4:C21)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H21" s="14" t="str">
         <f t="shared" si="1"/>
@@ -1394,7 +1400,7 @@
       </c>
       <c r="J21" s="14">
         <f>AVERAGE($E$4:E21)</f>
-        <v>8.2777777777777786</v>
+        <v>14</v>
       </c>
       <c r="K21" s="11"/>
     </row>
@@ -1414,7 +1420,7 @@
       <c r="F22" s="6"/>
       <c r="G22" s="9">
         <f>SUM($C$4:C22)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H22" s="9" t="str">
         <f t="shared" si="1"/>
@@ -1426,7 +1432,7 @@
       </c>
       <c r="J22" s="9">
         <f>AVERAGE($E$4:E22)</f>
-        <v>7.6842105263157894</v>
+        <v>13.105263157894736</v>
       </c>
       <c r="K22" s="11"/>
     </row>
@@ -1446,7 +1452,7 @@
       <c r="F23" s="6"/>
       <c r="G23" s="14">
         <f>SUM($C$4:C23)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H23" s="14" t="str">
         <f t="shared" si="1"/>
@@ -1458,7 +1464,7 @@
       </c>
       <c r="J23" s="14">
         <f>AVERAGE($E$4:E23)</f>
-        <v>7.15</v>
+        <v>12.3</v>
       </c>
       <c r="K23" s="11"/>
     </row>
@@ -1478,7 +1484,7 @@
       <c r="F24" s="6"/>
       <c r="G24" s="9">
         <f>SUM($C$4:C24)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H24" s="9" t="str">
         <f t="shared" si="1"/>
@@ -1490,7 +1496,7 @@
       </c>
       <c r="J24" s="9">
         <f>AVERAGE($E$4:E24)</f>
-        <v>6.666666666666667</v>
+        <v>11.571428571428571</v>
       </c>
       <c r="K24" s="11"/>
     </row>
@@ -1510,7 +1516,7 @@
       <c r="F25" s="6"/>
       <c r="G25" s="14">
         <f>SUM($C$4:C25)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H25" s="14" t="str">
         <f t="shared" si="1"/>
@@ -1522,7 +1528,7 @@
       </c>
       <c r="J25" s="14">
         <f>AVERAGE($E$4:E25)</f>
-        <v>6.2272727272727275</v>
+        <v>10.909090909090908</v>
       </c>
       <c r="K25" s="11"/>
     </row>
@@ -1542,7 +1548,7 @@
       <c r="F26" s="6"/>
       <c r="G26" s="9">
         <f>SUM($C$4:C26)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H26" s="9" t="str">
         <f t="shared" si="1"/>
@@ -1554,7 +1560,7 @@
       </c>
       <c r="J26" s="9">
         <f>AVERAGE($E$4:E26)</f>
-        <v>5.8260869565217392</v>
+        <v>10.304347826086957</v>
       </c>
       <c r="K26" s="11"/>
     </row>
@@ -1574,7 +1580,7 @@
       <c r="F27" s="6"/>
       <c r="G27" s="14">
         <f>SUM($C$4:C27)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H27" s="14" t="str">
         <f t="shared" si="1"/>
@@ -1586,7 +1592,7 @@
       </c>
       <c r="J27" s="14">
         <f>AVERAGE($E$4:E27)</f>
-        <v>5.458333333333333</v>
+        <v>9.75</v>
       </c>
       <c r="K27" s="11"/>
     </row>
@@ -1606,7 +1612,7 @@
       <c r="F28" s="6"/>
       <c r="G28" s="9">
         <f>SUM($C$4:C28)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H28" s="9" t="str">
         <f t="shared" si="1"/>
@@ -1618,7 +1624,7 @@
       </c>
       <c r="J28" s="9">
         <f>AVERAGE($E$4:E28)</f>
-        <v>5.12</v>
+        <v>9.24</v>
       </c>
       <c r="K28" s="11"/>
     </row>
@@ -1638,7 +1644,7 @@
       <c r="F29" s="6"/>
       <c r="G29" s="14">
         <f>SUM($C$4:C29)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H29" s="14" t="str">
         <f t="shared" si="1"/>
@@ -1650,7 +1656,7 @@
       </c>
       <c r="J29" s="14">
         <f>AVERAGE($E$4:E29)</f>
-        <v>4.8076923076923075</v>
+        <v>8.7692307692307701</v>
       </c>
       <c r="K29" s="11"/>
     </row>
@@ -1670,7 +1676,7 @@
       <c r="F30" s="6"/>
       <c r="G30" s="9">
         <f>SUM($C$4:C30)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H30" s="9" t="str">
         <f t="shared" si="1"/>
@@ -1682,7 +1688,7 @@
       </c>
       <c r="J30" s="9">
         <f>AVERAGE($E$4:E30)</f>
-        <v>4.5185185185185182</v>
+        <v>8.3333333333333339</v>
       </c>
       <c r="K30" s="11"/>
     </row>
@@ -1702,7 +1708,7 @@
       <c r="F31" s="6"/>
       <c r="G31" s="14">
         <f>SUM($C$4:C31)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H31" s="14" t="str">
         <f t="shared" si="1"/>
@@ -1714,7 +1720,7 @@
       </c>
       <c r="J31" s="14">
         <f>AVERAGE($E$4:E31)</f>
-        <v>4.25</v>
+        <v>7.9285714285714288</v>
       </c>
       <c r="K31" s="11"/>
     </row>
@@ -1734,7 +1740,7 @@
       <c r="F32" s="6"/>
       <c r="G32" s="9">
         <f>SUM($C$4:C32)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H32" s="9" t="str">
         <f t="shared" si="1"/>
@@ -1746,7 +1752,7 @@
       </c>
       <c r="J32" s="9">
         <f>AVERAGE($E$4:E32)</f>
-        <v>4</v>
+        <v>7.5517241379310347</v>
       </c>
       <c r="K32" s="11"/>
     </row>
@@ -1766,7 +1772,7 @@
       <c r="F33" s="6"/>
       <c r="G33" s="14">
         <f>SUM($C$4:C33)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H33" s="14" t="str">
         <f t="shared" si="1"/>
@@ -1778,7 +1784,7 @@
       </c>
       <c r="J33" s="14">
         <f>AVERAGE($E$4:E33)</f>
-        <v>3.7666666666666666</v>
+        <v>7.2</v>
       </c>
       <c r="K33" s="11"/>
     </row>
@@ -1798,7 +1804,7 @@
       <c r="F34" s="6"/>
       <c r="G34" s="9">
         <f>SUM($C$4:C34)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H34" s="9" t="str">
         <f t="shared" si="1"/>
@@ -1810,7 +1816,7 @@
       </c>
       <c r="J34" s="9">
         <f>AVERAGE($E$4:E34)</f>
-        <v>3.5483870967741935</v>
+        <v>6.870967741935484</v>
       </c>
       <c r="K34" s="11"/>
     </row>
@@ -1830,7 +1836,7 @@
       <c r="F35" s="6"/>
       <c r="G35" s="14">
         <f>SUM($C$4:C35)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H35" s="14" t="str">
         <f t="shared" si="1"/>
@@ -1842,7 +1848,7 @@
       </c>
       <c r="J35" s="14">
         <f>AVERAGE($E$4:E35)</f>
-        <v>3.34375</v>
+        <v>6.5625</v>
       </c>
       <c r="K35" s="11"/>
     </row>
@@ -1862,7 +1868,7 @@
       <c r="F36" s="6"/>
       <c r="G36" s="9">
         <f>SUM($C$4:C36)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H36" s="9" t="str">
         <f t="shared" ref="H36:H63" si="4">IF(F36="","",F36-G36)</f>
@@ -1874,7 +1880,7 @@
       </c>
       <c r="J36" s="9">
         <f>AVERAGE($E$4:E36)</f>
-        <v>3.1515151515151514</v>
+        <v>6.2727272727272725</v>
       </c>
       <c r="K36" s="11"/>
     </row>
@@ -1894,7 +1900,7 @@
       <c r="F37" s="6"/>
       <c r="G37" s="14">
         <f>SUM($C$4:C37)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H37" s="14" t="str">
         <f t="shared" si="4"/>
@@ -1906,7 +1912,7 @@
       </c>
       <c r="J37" s="14">
         <f>AVERAGE($E$4:E37)</f>
-        <v>2.9705882352941178</v>
+        <v>6</v>
       </c>
       <c r="K37" s="11"/>
     </row>
@@ -1926,7 +1932,7 @@
       <c r="F38" s="6"/>
       <c r="G38" s="9">
         <f>SUM($C$4:C38)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H38" s="9" t="str">
         <f t="shared" si="4"/>
@@ -1938,7 +1944,7 @@
       </c>
       <c r="J38" s="9">
         <f>AVERAGE($E$4:E38)</f>
-        <v>2.8</v>
+        <v>5.7428571428571429</v>
       </c>
       <c r="K38" s="11"/>
     </row>
@@ -1958,7 +1964,7 @@
       <c r="F39" s="6"/>
       <c r="G39" s="14">
         <f>SUM($C$4:C39)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H39" s="14" t="str">
         <f t="shared" si="4"/>
@@ -1970,7 +1976,7 @@
       </c>
       <c r="J39" s="14">
         <f>AVERAGE($E$4:E39)</f>
-        <v>2.6388888888888888</v>
+        <v>5.5</v>
       </c>
       <c r="K39" s="11"/>
     </row>
@@ -1990,7 +1996,7 @@
       <c r="F40" s="6"/>
       <c r="G40" s="9">
         <f>SUM($C$4:C40)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H40" s="9" t="str">
         <f t="shared" si="4"/>
@@ -2002,7 +2008,7 @@
       </c>
       <c r="J40" s="9">
         <f>AVERAGE($E$4:E40)</f>
-        <v>2.4864864864864864</v>
+        <v>5.2702702702702702</v>
       </c>
       <c r="K40" s="11"/>
     </row>
@@ -2022,7 +2028,7 @@
       <c r="F41" s="6"/>
       <c r="G41" s="14">
         <f>SUM($C$4:C41)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H41" s="14" t="str">
         <f t="shared" si="4"/>
@@ -2034,7 +2040,7 @@
       </c>
       <c r="J41" s="14">
         <f>AVERAGE($E$4:E41)</f>
-        <v>2.3421052631578947</v>
+        <v>5.0526315789473681</v>
       </c>
       <c r="K41" s="11"/>
     </row>
@@ -2054,7 +2060,7 @@
       <c r="F42" s="6"/>
       <c r="G42" s="9">
         <f>SUM($C$4:C42)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H42" s="9" t="str">
         <f t="shared" si="4"/>
@@ -2066,7 +2072,7 @@
       </c>
       <c r="J42" s="9">
         <f>AVERAGE($E$4:E42)</f>
-        <v>2.2051282051282053</v>
+        <v>4.8461538461538458</v>
       </c>
       <c r="K42" s="11"/>
     </row>
@@ -2086,7 +2092,7 @@
       <c r="F43" s="6"/>
       <c r="G43" s="14">
         <f>SUM($C$4:C43)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H43" s="14" t="str">
         <f t="shared" si="4"/>
@@ -2098,7 +2104,7 @@
       </c>
       <c r="J43" s="14">
         <f>AVERAGE($E$4:E43)</f>
-        <v>2.0750000000000002</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="K43" s="11"/>
     </row>
@@ -2118,7 +2124,7 @@
       <c r="F44" s="6"/>
       <c r="G44" s="9">
         <f>SUM($C$4:C44)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H44" s="9" t="str">
         <f t="shared" si="4"/>
@@ -2130,7 +2136,7 @@
       </c>
       <c r="J44" s="9">
         <f>AVERAGE($E$4:E44)</f>
-        <v>1.9512195121951219</v>
+        <v>4.4634146341463419</v>
       </c>
       <c r="K44" s="11"/>
     </row>
@@ -2150,7 +2156,7 @@
       <c r="F45" s="6"/>
       <c r="G45" s="14">
         <f>SUM($C$4:C45)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H45" s="14" t="str">
         <f t="shared" si="4"/>
@@ -2162,7 +2168,7 @@
       </c>
       <c r="J45" s="14">
         <f>AVERAGE($E$4:E45)</f>
-        <v>1.8333333333333333</v>
+        <v>4.2857142857142856</v>
       </c>
       <c r="K45" s="11"/>
     </row>
@@ -2182,7 +2188,7 @@
       <c r="F46" s="6"/>
       <c r="G46" s="9">
         <f>SUM($C$4:C46)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H46" s="9" t="str">
         <f t="shared" si="4"/>
@@ -2194,7 +2200,7 @@
       </c>
       <c r="J46" s="9">
         <f>AVERAGE($E$4:E46)</f>
-        <v>1.7209302325581395</v>
+        <v>4.1162790697674421</v>
       </c>
       <c r="K46" s="11"/>
     </row>
@@ -2214,7 +2220,7 @@
       <c r="F47" s="6"/>
       <c r="G47" s="14">
         <f>SUM($C$4:C47)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H47" s="14" t="str">
         <f t="shared" si="4"/>
@@ -2226,7 +2232,7 @@
       </c>
       <c r="J47" s="14">
         <f>AVERAGE($E$4:E47)</f>
-        <v>1.6136363636363635</v>
+        <v>3.9545454545454546</v>
       </c>
       <c r="K47" s="11"/>
     </row>
@@ -2246,7 +2252,7 @@
       <c r="F48" s="6"/>
       <c r="G48" s="9">
         <f>SUM($C$4:C48)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H48" s="9" t="str">
         <f t="shared" si="4"/>
@@ -2258,7 +2264,7 @@
       </c>
       <c r="J48" s="9">
         <f>AVERAGE($E$4:E48)</f>
-        <v>1.5111111111111111</v>
+        <v>3.8</v>
       </c>
       <c r="K48" s="11"/>
     </row>
@@ -2278,7 +2284,7 @@
       <c r="F49" s="6"/>
       <c r="G49" s="14">
         <f>SUM($C$4:C49)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H49" s="14" t="str">
         <f t="shared" si="4"/>
@@ -2290,7 +2296,7 @@
       </c>
       <c r="J49" s="14">
         <f>AVERAGE($E$4:E49)</f>
-        <v>1.4130434782608696</v>
+        <v>3.652173913043478</v>
       </c>
       <c r="K49" s="11"/>
     </row>
@@ -2310,7 +2316,7 @@
       <c r="F50" s="6"/>
       <c r="G50" s="9">
         <f>SUM($C$4:C50)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H50" s="9" t="str">
         <f t="shared" si="4"/>
@@ -2322,7 +2328,7 @@
       </c>
       <c r="J50" s="9">
         <f>AVERAGE($E$4:E50)</f>
-        <v>1.3191489361702127</v>
+        <v>3.5106382978723403</v>
       </c>
       <c r="K50" s="11"/>
     </row>
@@ -2342,7 +2348,7 @@
       <c r="F51" s="6"/>
       <c r="G51" s="14">
         <f>SUM($C$4:C51)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H51" s="14" t="str">
         <f t="shared" si="4"/>
@@ -2354,7 +2360,7 @@
       </c>
       <c r="J51" s="14">
         <f>AVERAGE($E$4:E51)</f>
-        <v>1.2291666666666667</v>
+        <v>3.375</v>
       </c>
       <c r="K51" s="11"/>
     </row>
@@ -2374,7 +2380,7 @@
       <c r="F52" s="6"/>
       <c r="G52" s="9">
         <f>SUM($C$4:C52)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H52" s="9" t="str">
         <f t="shared" si="4"/>
@@ -2386,7 +2392,7 @@
       </c>
       <c r="J52" s="9">
         <f>AVERAGE($E$4:E52)</f>
-        <v>1.1428571428571428</v>
+        <v>3.2448979591836733</v>
       </c>
       <c r="K52" s="11"/>
     </row>
@@ -2406,7 +2412,7 @@
       <c r="F53" s="6"/>
       <c r="G53" s="14">
         <f>SUM($C$4:C53)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H53" s="14" t="str">
         <f t="shared" si="4"/>
@@ -2418,7 +2424,7 @@
       </c>
       <c r="J53" s="14">
         <f>AVERAGE($E$4:E53)</f>
-        <v>1.06</v>
+        <v>3.12</v>
       </c>
       <c r="K53" s="11"/>
     </row>
@@ -2438,7 +2444,7 @@
       <c r="F54" s="6"/>
       <c r="G54" s="9">
         <f>SUM($C$4:C54)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H54" s="9" t="str">
         <f t="shared" si="4"/>
@@ -2450,7 +2456,7 @@
       </c>
       <c r="J54" s="9">
         <f>AVERAGE($E$4:E54)</f>
-        <v>0.98039215686274506</v>
+        <v>3</v>
       </c>
       <c r="K54" s="11"/>
     </row>
@@ -2470,7 +2476,7 @@
       <c r="F55" s="6"/>
       <c r="G55" s="14">
         <f>SUM($C$4:C55)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H55" s="14" t="str">
         <f t="shared" si="4"/>
@@ -2482,7 +2488,7 @@
       </c>
       <c r="J55" s="14">
         <f>AVERAGE($E$4:E55)</f>
-        <v>0.90384615384615385</v>
+        <v>2.8846153846153846</v>
       </c>
       <c r="K55" s="11"/>
     </row>
@@ -2502,7 +2508,7 @@
       <c r="F56" s="6"/>
       <c r="G56" s="9">
         <f>SUM($C$4:C56)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H56" s="9" t="str">
         <f t="shared" si="4"/>
@@ -2514,7 +2520,7 @@
       </c>
       <c r="J56" s="9">
         <f>AVERAGE($E$4:E56)</f>
-        <v>0.83018867924528306</v>
+        <v>2.7735849056603774</v>
       </c>
       <c r="K56" s="11"/>
     </row>
@@ -2534,7 +2540,7 @@
       <c r="F57" s="6"/>
       <c r="G57" s="14">
         <f>SUM($C$4:C57)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H57" s="14" t="str">
         <f t="shared" si="4"/>
@@ -2546,7 +2552,7 @@
       </c>
       <c r="J57" s="14">
         <f>AVERAGE($E$4:E57)</f>
-        <v>0.7592592592592593</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="K57" s="11"/>
     </row>
@@ -2566,7 +2572,7 @@
       <c r="F58" s="6"/>
       <c r="G58" s="9">
         <f>SUM($C$4:C58)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H58" s="9" t="str">
         <f t="shared" si="4"/>
@@ -2578,7 +2584,7 @@
       </c>
       <c r="J58" s="9">
         <f>AVERAGE($E$4:E58)</f>
-        <v>0.69090909090909092</v>
+        <v>2.5636363636363635</v>
       </c>
       <c r="K58" s="11"/>
     </row>
@@ -2598,7 +2604,7 @@
       <c r="F59" s="6"/>
       <c r="G59" s="14">
         <f>SUM($C$4:C59)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H59" s="14" t="str">
         <f t="shared" si="4"/>
@@ -2610,7 +2616,7 @@
       </c>
       <c r="J59" s="14">
         <f>AVERAGE($E$4:E59)</f>
-        <v>0.625</v>
+        <v>2.4642857142857144</v>
       </c>
       <c r="K59" s="11"/>
     </row>
@@ -2630,7 +2636,7 @@
       <c r="F60" s="6"/>
       <c r="G60" s="9">
         <f>SUM($C$4:C60)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H60" s="9" t="str">
         <f t="shared" si="4"/>
@@ -2642,7 +2648,7 @@
       </c>
       <c r="J60" s="9">
         <f>AVERAGE($E$4:E60)</f>
-        <v>0.56140350877192979</v>
+        <v>2.3684210526315788</v>
       </c>
       <c r="K60" s="11"/>
     </row>
@@ -2662,7 +2668,7 @@
       <c r="F61" s="6"/>
       <c r="G61" s="14">
         <f>SUM($C$4:C61)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H61" s="14" t="str">
         <f t="shared" si="4"/>
@@ -2674,7 +2680,7 @@
       </c>
       <c r="J61" s="14">
         <f>AVERAGE($E$4:E61)</f>
-        <v>0.5</v>
+        <v>2.2758620689655173</v>
       </c>
       <c r="K61" s="11"/>
     </row>
@@ -2694,7 +2700,7 @@
       <c r="F62" s="6"/>
       <c r="G62" s="9">
         <f>SUM($C$4:C62)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H62" s="9" t="str">
         <f t="shared" si="4"/>
@@ -2706,7 +2712,7 @@
       </c>
       <c r="J62" s="9">
         <f>AVERAGE($E$4:E62)</f>
-        <v>0.44067796610169491</v>
+        <v>2.1864406779661016</v>
       </c>
       <c r="K62" s="11"/>
     </row>
@@ -2726,7 +2732,7 @@
       <c r="F63" s="6"/>
       <c r="G63" s="14">
         <f>SUM($C$4:C63)</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="H63" s="14" t="str">
         <f t="shared" si="4"/>
@@ -2738,7 +2744,7 @@
       </c>
       <c r="J63" s="14">
         <f>AVERAGE($E$4:E63)</f>
-        <v>0.38333333333333336</v>
+        <v>2.1</v>
       </c>
       <c r="K63" s="11"/>
     </row>
@@ -2804,7 +2810,7 @@
       </c>
       <c r="B4" s="18">
         <f>IFERROR(LOOKUP(2,1/(Registro_Mensual!G4:G63&lt;&gt;""),Registro_Mensual!G4:G63),"")</f>
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="D4" s="33" t="s">
         <v>21</v>
@@ -2817,14 +2823,14 @@
       </c>
       <c r="B5" s="18">
         <f ca="1">OFFSET(Registro_Mensual!F3,COUNTA(Registro_Mensual!F4:F63),0)</f>
-        <v>213</v>
+        <v>319</v>
       </c>
       <c r="D5" s="17" t="s">
         <v>23</v>
       </c>
       <c r="E5" s="18">
         <f>B8</f>
-        <v>98.5</v>
+        <v>99</v>
       </c>
       <c r="F5" s="19"/>
       <c r="G5" s="19"/>
@@ -2835,7 +2841,7 @@
       </c>
       <c r="B6" s="18">
         <f ca="1">IFERROR(B5-B4,"")</f>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>25</v>
@@ -2852,22 +2858,22 @@
       </c>
       <c r="B7" s="21">
         <f ca="1">IFERROR(B5/B4-1,"")</f>
-        <v>4.9261083743842304E-2</v>
+        <v>4.2483660130719025E-2</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>27</v>
       </c>
       <c r="E7" s="18">
         <f>E5*((1+E6/12)^60-1)/(E6/12)</f>
-        <v>7237.4703401562301</v>
+        <v>7274.2087682788506</v>
       </c>
       <c r="F7" s="23">
         <f>E5*60</f>
-        <v>5910</v>
+        <v>5940</v>
       </c>
       <c r="G7" s="23">
         <f>E7-F7</f>
-        <v>1327.4703401562301</v>
+        <v>1334.2087682788506</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2876,22 +2882,22 @@
       </c>
       <c r="B8" s="18">
         <f>IFERROR(AVERAGEIF(Registro_Mensual!C4:C63,"&gt;0",Registro_Mensual!E4:E63),"")</f>
-        <v>98.5</v>
+        <v>99</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>29</v>
       </c>
       <c r="E8" s="18">
         <f>E5*((1+E6/12)^120-1)/(E6/12)</f>
-        <v>18020.184465398153</v>
+        <v>18111.657482989005</v>
       </c>
       <c r="F8" s="23">
         <f>E5*120</f>
-        <v>11820</v>
+        <v>11880</v>
       </c>
       <c r="G8" s="23">
         <f>E8-F8</f>
-        <v>6200.1844653981534</v>
+        <v>6231.6574829890051</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2900,22 +2906,22 @@
       </c>
       <c r="B9" s="22">
         <f>COUNTIF(Registro_Mensual!C4:C63,"&gt;0")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" s="17" t="s">
         <v>31</v>
       </c>
       <c r="E9" s="18">
         <f>E5*((1+E6/12)^240-1)/(E6/12)</f>
-        <v>58018.510938713524</v>
+        <v>58313.021146524254</v>
       </c>
       <c r="F9" s="23">
         <f>E5*240</f>
-        <v>23640</v>
+        <v>23760</v>
       </c>
       <c r="G9" s="23">
         <f>E9-F9</f>
-        <v>34378.510938713524</v>
+        <v>34553.021146524254</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2928,15 +2934,15 @@
       </c>
       <c r="E10" s="18">
         <f>E5*((1+E6/12)^360-1)/(E6/12)</f>
-        <v>146800.4056933393</v>
+        <v>147545.58541767095</v>
       </c>
       <c r="F10" s="23">
         <f>E5*360</f>
-        <v>35460</v>
+        <v>35640</v>
       </c>
       <c r="G10" s="23">
         <f>E10-F10</f>
-        <v>111340.4056933393</v>
+        <v>111905.58541767095</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2947,15 +2953,15 @@
       </c>
       <c r="E11" s="18">
         <f>E5*((1+E6/12)^480-1)/(E6/12)</f>
-        <v>343864.27138982102</v>
+        <v>345609.77530550543</v>
       </c>
       <c r="F11" s="23">
         <f>E5*480</f>
-        <v>47280</v>
+        <v>47520</v>
       </c>
       <c r="G11" s="23">
         <f>E11-F11</f>
-        <v>296584.27138982102</v>
+        <v>298089.77530550543</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">

--- a/inversiones.xlsx
+++ b/inversiones.xlsx
@@ -1,23 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marag\OneDrive\Documentos\GitHub\inversiones\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marag\Documents\GitHub\inversiones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB0799A5-AE6D-439D-AEAD-F1D3C252CAB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A8F11B1-AA28-48F6-AE24-7A44738EBC4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro_Mensual" sheetId="1" r:id="rId1"/>
     <sheet name="Resumen" sheetId="2" r:id="rId2"/>
+    <sheet name="Beneficios bolsa" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -26,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="51">
   <si>
     <t>📈 SEGUIMIENTO DE INVERSIONES — S&amp;P 500</t>
   </si>
@@ -162,17 +175,47 @@
   </si>
   <si>
     <t>En 40 años tendrías aprox.</t>
+  </si>
+  <si>
+    <t>Coca Cola</t>
+  </si>
+  <si>
+    <t>2026 TOTAL</t>
+  </si>
+  <si>
+    <t>Allianz</t>
+  </si>
+  <si>
+    <t>SP500</t>
+  </si>
+  <si>
+    <t>Mercado</t>
+  </si>
+  <si>
+    <t>Registro 2026</t>
+  </si>
+  <si>
+    <t>Balance</t>
+  </si>
+  <si>
+    <t>Fecha venta</t>
+  </si>
+  <si>
+    <t>Balance 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="5">
+    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="#,##0.00&quot; €&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="173" formatCode="_-* #,##0\ &quot;€&quot;_-;\-* #,##0\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
+    <numFmt numFmtId="174" formatCode="_-* #,##0.00\ [$€-C0A]_-;\-* #,##0.00\ [$€-C0A]_-;_-* &quot;-&quot;??\ [$€-C0A]_-;_-@_-"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -274,8 +317,15 @@
       <name val="Arial"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -336,8 +386,20 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -373,11 +435,97 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -450,6 +598,15 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -463,20 +620,115 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="173" fontId="0" fillId="11" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="7">
+    <dxf>
+      <numFmt numFmtId="174" formatCode="_-* #,##0.00\ [$€-C0A]_-;\-* #,##0.00\ [$€-C0A]_-;_-* &quot;-&quot;??\ [$€-C0A]_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="21" formatCode="dd\-mmm"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="173" formatCode="_-* #,##0\ &quot;€&quot;_-;\-* #,##0\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -555,6 +807,29 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{43361EA0-38CE-405F-999E-E678479A76FE}" name="Tabla3" displayName="Tabla3" ref="B2:C11" totalsRowShown="0" headerRowBorderDxfId="5" tableBorderDxfId="6" totalsRowBorderDxfId="4">
+  <autoFilter ref="B2:C11" xr:uid="{43361EA0-38CE-405F-999E-E678479A76FE}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{5452176F-36B8-4CDD-9F33-5D70AA66A550}" name="Mercado" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{AA88D4F0-70F9-4823-81E5-D366BE0621A3}" name="Balance" dataDxfId="2" dataCellStyle="Moneda"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E0EF1798-5DBC-4CC2-BF2B-D1627830BBD8}" name="Tabla4" displayName="Tabla4" ref="E2:G6" totalsRowShown="0">
+  <autoFilter ref="E2:G6" xr:uid="{E0EF1798-5DBC-4CC2-BF2B-D1627830BBD8}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{D7244F53-013B-49D1-84D7-0E66C32F39B4}" name="Mercado"/>
+    <tableColumn id="2" xr3:uid="{28786B65-FA4E-4DA6-9569-A775903889EB}" name="Fecha venta" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{00894C4B-3E6A-4755-9F14-59B8AD97246A}" name="Balance" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -928,31 +1203,37 @@
       <c r="A7" s="12">
         <v>4</v>
       </c>
-      <c r="B7" s="13"/>
-      <c r="C7" s="6"/>
+      <c r="B7" s="5">
+        <v>46175</v>
+      </c>
+      <c r="C7" s="6">
+        <v>100</v>
+      </c>
       <c r="D7" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E7" s="8">
         <f t="shared" si="0"/>
-        <v>-3</v>
-      </c>
-      <c r="F7" s="6"/>
+        <v>100</v>
+      </c>
+      <c r="F7" s="6">
+        <v>420</v>
+      </c>
       <c r="G7" s="14">
         <f>SUM($C$4:C7)</f>
-        <v>306</v>
-      </c>
-      <c r="H7" s="14" t="str">
+        <v>406</v>
+      </c>
+      <c r="H7" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I7" s="15" t="str">
+        <v>14</v>
+      </c>
+      <c r="I7" s="15">
         <f t="shared" si="2"/>
-        <v/>
+        <v>3.4482758620689724E-2</v>
       </c>
       <c r="J7" s="14">
         <f>AVERAGE($E$4:E7)</f>
-        <v>73.5</v>
+        <v>99.25</v>
       </c>
       <c r="K7" s="11"/>
     </row>
@@ -963,16 +1244,16 @@
       <c r="B8" s="13"/>
       <c r="C8" s="6"/>
       <c r="D8" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E8" s="8">
         <f t="shared" si="0"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F8" s="6"/>
       <c r="G8" s="9">
         <f>SUM($C$4:C8)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H8" s="9" t="str">
         <f t="shared" si="1"/>
@@ -984,7 +1265,7 @@
       </c>
       <c r="J8" s="9">
         <f>AVERAGE($E$4:E8)</f>
-        <v>58.2</v>
+        <v>79.400000000000006</v>
       </c>
       <c r="K8" s="11"/>
     </row>
@@ -995,16 +1276,16 @@
       <c r="B9" s="13"/>
       <c r="C9" s="6"/>
       <c r="D9" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E9" s="8">
         <f t="shared" si="0"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="14">
         <f>SUM($C$4:C9)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H9" s="14" t="str">
         <f t="shared" si="1"/>
@@ -1016,7 +1297,7 @@
       </c>
       <c r="J9" s="14">
         <f>AVERAGE($E$4:E9)</f>
-        <v>48</v>
+        <v>66.166666666666671</v>
       </c>
       <c r="K9" s="11"/>
     </row>
@@ -1027,16 +1308,16 @@
       <c r="B10" s="13"/>
       <c r="C10" s="6"/>
       <c r="D10" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E10" s="8">
         <f t="shared" si="0"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F10" s="6"/>
       <c r="G10" s="9">
         <f>SUM($C$4:C10)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H10" s="9" t="str">
         <f t="shared" si="1"/>
@@ -1048,7 +1329,7 @@
       </c>
       <c r="J10" s="9">
         <f>AVERAGE($E$4:E10)</f>
-        <v>40.714285714285715</v>
+        <v>56.714285714285715</v>
       </c>
       <c r="K10" s="11"/>
     </row>
@@ -1059,16 +1340,16 @@
       <c r="B11" s="13"/>
       <c r="C11" s="6"/>
       <c r="D11" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E11" s="8">
         <f t="shared" si="0"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F11" s="6"/>
       <c r="G11" s="14">
         <f>SUM($C$4:C11)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H11" s="14" t="str">
         <f t="shared" si="1"/>
@@ -1080,7 +1361,7 @@
       </c>
       <c r="J11" s="14">
         <f>AVERAGE($E$4:E11)</f>
-        <v>35.25</v>
+        <v>49.625</v>
       </c>
       <c r="K11" s="11"/>
     </row>
@@ -1091,16 +1372,16 @@
       <c r="B12" s="13"/>
       <c r="C12" s="6"/>
       <c r="D12" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E12" s="8">
         <f t="shared" si="0"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="9">
         <f>SUM($C$4:C12)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H12" s="9" t="str">
         <f t="shared" si="1"/>
@@ -1112,7 +1393,7 @@
       </c>
       <c r="J12" s="9">
         <f>AVERAGE($E$4:E12)</f>
-        <v>31</v>
+        <v>44.111111111111114</v>
       </c>
       <c r="K12" s="11"/>
     </row>
@@ -1123,16 +1404,16 @@
       <c r="B13" s="13"/>
       <c r="C13" s="6"/>
       <c r="D13" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E13" s="8">
         <f t="shared" si="0"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F13" s="6"/>
       <c r="G13" s="14">
         <f>SUM($C$4:C13)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H13" s="14" t="str">
         <f t="shared" si="1"/>
@@ -1144,7 +1425,7 @@
       </c>
       <c r="J13" s="14">
         <f>AVERAGE($E$4:E13)</f>
-        <v>27.6</v>
+        <v>39.700000000000003</v>
       </c>
       <c r="K13" s="11"/>
     </row>
@@ -1155,16 +1436,16 @@
       <c r="B14" s="13"/>
       <c r="C14" s="6"/>
       <c r="D14" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E14" s="8">
         <f t="shared" si="0"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F14" s="6"/>
       <c r="G14" s="9">
         <f>SUM($C$4:C14)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H14" s="9" t="str">
         <f t="shared" si="1"/>
@@ -1176,7 +1457,7 @@
       </c>
       <c r="J14" s="9">
         <f>AVERAGE($E$4:E14)</f>
-        <v>24.818181818181817</v>
+        <v>36.090909090909093</v>
       </c>
       <c r="K14" s="11"/>
     </row>
@@ -1187,16 +1468,16 @@
       <c r="B15" s="13"/>
       <c r="C15" s="6"/>
       <c r="D15" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E15" s="8">
         <f t="shared" si="0"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F15" s="6"/>
       <c r="G15" s="14">
         <f>SUM($C$4:C15)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H15" s="14" t="str">
         <f t="shared" si="1"/>
@@ -1208,7 +1489,7 @@
       </c>
       <c r="J15" s="14">
         <f>AVERAGE($E$4:E15)</f>
-        <v>22.5</v>
+        <v>33.083333333333336</v>
       </c>
       <c r="K15" s="11"/>
     </row>
@@ -1219,16 +1500,16 @@
       <c r="B16" s="13"/>
       <c r="C16" s="6"/>
       <c r="D16" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E16" s="8">
         <f t="shared" si="0"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="9">
         <f>SUM($C$4:C16)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H16" s="9" t="str">
         <f t="shared" si="1"/>
@@ -1240,7 +1521,7 @@
       </c>
       <c r="J16" s="9">
         <f>AVERAGE($E$4:E16)</f>
-        <v>20.53846153846154</v>
+        <v>30.53846153846154</v>
       </c>
       <c r="K16" s="11"/>
     </row>
@@ -1251,16 +1532,16 @@
       <c r="B17" s="13"/>
       <c r="C17" s="6"/>
       <c r="D17" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E17" s="8">
         <f t="shared" si="0"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F17" s="6"/>
       <c r="G17" s="14">
         <f>SUM($C$4:C17)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H17" s="14" t="str">
         <f t="shared" si="1"/>
@@ -1272,7 +1553,7 @@
       </c>
       <c r="J17" s="14">
         <f>AVERAGE($E$4:E17)</f>
-        <v>18.857142857142858</v>
+        <v>28.357142857142858</v>
       </c>
       <c r="K17" s="11"/>
     </row>
@@ -1283,16 +1564,16 @@
       <c r="B18" s="13"/>
       <c r="C18" s="6"/>
       <c r="D18" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E18" s="8">
         <f t="shared" si="0"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F18" s="6"/>
       <c r="G18" s="9">
         <f>SUM($C$4:C18)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H18" s="9" t="str">
         <f t="shared" si="1"/>
@@ -1304,7 +1585,7 @@
       </c>
       <c r="J18" s="9">
         <f>AVERAGE($E$4:E18)</f>
-        <v>17.399999999999999</v>
+        <v>26.466666666666665</v>
       </c>
       <c r="K18" s="11"/>
     </row>
@@ -1315,16 +1596,16 @@
       <c r="B19" s="13"/>
       <c r="C19" s="6"/>
       <c r="D19" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E19" s="8">
         <f t="shared" si="0"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F19" s="6"/>
       <c r="G19" s="14">
         <f>SUM($C$4:C19)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H19" s="14" t="str">
         <f t="shared" si="1"/>
@@ -1336,7 +1617,7 @@
       </c>
       <c r="J19" s="14">
         <f>AVERAGE($E$4:E19)</f>
-        <v>16.125</v>
+        <v>24.8125</v>
       </c>
       <c r="K19" s="11"/>
     </row>
@@ -1347,16 +1628,16 @@
       <c r="B20" s="13"/>
       <c r="C20" s="6"/>
       <c r="D20" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E20" s="8">
         <f t="shared" si="0"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F20" s="6"/>
       <c r="G20" s="9">
         <f>SUM($C$4:C20)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H20" s="9" t="str">
         <f t="shared" si="1"/>
@@ -1368,7 +1649,7 @@
       </c>
       <c r="J20" s="9">
         <f>AVERAGE($E$4:E20)</f>
-        <v>15</v>
+        <v>23.352941176470587</v>
       </c>
       <c r="K20" s="11"/>
     </row>
@@ -1379,16 +1660,16 @@
       <c r="B21" s="13"/>
       <c r="C21" s="6"/>
       <c r="D21" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E21" s="8">
         <f t="shared" si="0"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F21" s="6"/>
       <c r="G21" s="14">
         <f>SUM($C$4:C21)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H21" s="14" t="str">
         <f t="shared" si="1"/>
@@ -1400,7 +1681,7 @@
       </c>
       <c r="J21" s="14">
         <f>AVERAGE($E$4:E21)</f>
-        <v>14</v>
+        <v>22.055555555555557</v>
       </c>
       <c r="K21" s="11"/>
     </row>
@@ -1411,16 +1692,16 @@
       <c r="B22" s="13"/>
       <c r="C22" s="6"/>
       <c r="D22" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E22" s="8">
         <f t="shared" si="0"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="9">
         <f>SUM($C$4:C22)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H22" s="9" t="str">
         <f t="shared" si="1"/>
@@ -1432,7 +1713,7 @@
       </c>
       <c r="J22" s="9">
         <f>AVERAGE($E$4:E22)</f>
-        <v>13.105263157894736</v>
+        <v>20.894736842105264</v>
       </c>
       <c r="K22" s="11"/>
     </row>
@@ -1443,16 +1724,16 @@
       <c r="B23" s="13"/>
       <c r="C23" s="6"/>
       <c r="D23" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E23" s="8">
         <f t="shared" si="0"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="14">
         <f>SUM($C$4:C23)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H23" s="14" t="str">
         <f t="shared" si="1"/>
@@ -1464,7 +1745,7 @@
       </c>
       <c r="J23" s="14">
         <f>AVERAGE($E$4:E23)</f>
-        <v>12.3</v>
+        <v>19.850000000000001</v>
       </c>
       <c r="K23" s="11"/>
     </row>
@@ -1475,16 +1756,16 @@
       <c r="B24" s="13"/>
       <c r="C24" s="6"/>
       <c r="D24" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E24" s="8">
         <f t="shared" si="0"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="9">
         <f>SUM($C$4:C24)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H24" s="9" t="str">
         <f t="shared" si="1"/>
@@ -1496,7 +1777,7 @@
       </c>
       <c r="J24" s="9">
         <f>AVERAGE($E$4:E24)</f>
-        <v>11.571428571428571</v>
+        <v>18.904761904761905</v>
       </c>
       <c r="K24" s="11"/>
     </row>
@@ -1507,16 +1788,16 @@
       <c r="B25" s="13"/>
       <c r="C25" s="6"/>
       <c r="D25" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E25" s="8">
         <f t="shared" si="0"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="14">
         <f>SUM($C$4:C25)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H25" s="14" t="str">
         <f t="shared" si="1"/>
@@ -1528,7 +1809,7 @@
       </c>
       <c r="J25" s="14">
         <f>AVERAGE($E$4:E25)</f>
-        <v>10.909090909090908</v>
+        <v>18.045454545454547</v>
       </c>
       <c r="K25" s="11"/>
     </row>
@@ -1539,16 +1820,16 @@
       <c r="B26" s="13"/>
       <c r="C26" s="6"/>
       <c r="D26" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E26" s="8">
         <f t="shared" si="0"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="9">
         <f>SUM($C$4:C26)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H26" s="9" t="str">
         <f t="shared" si="1"/>
@@ -1560,7 +1841,7 @@
       </c>
       <c r="J26" s="9">
         <f>AVERAGE($E$4:E26)</f>
-        <v>10.304347826086957</v>
+        <v>17.260869565217391</v>
       </c>
       <c r="K26" s="11"/>
     </row>
@@ -1571,16 +1852,16 @@
       <c r="B27" s="13"/>
       <c r="C27" s="6"/>
       <c r="D27" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E27" s="8">
         <f t="shared" si="0"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="14">
         <f>SUM($C$4:C27)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H27" s="14" t="str">
         <f t="shared" si="1"/>
@@ -1592,7 +1873,7 @@
       </c>
       <c r="J27" s="14">
         <f>AVERAGE($E$4:E27)</f>
-        <v>9.75</v>
+        <v>16.541666666666668</v>
       </c>
       <c r="K27" s="11"/>
     </row>
@@ -1603,16 +1884,16 @@
       <c r="B28" s="13"/>
       <c r="C28" s="6"/>
       <c r="D28" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E28" s="8">
         <f t="shared" si="0"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F28" s="6"/>
       <c r="G28" s="9">
         <f>SUM($C$4:C28)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H28" s="9" t="str">
         <f t="shared" si="1"/>
@@ -1624,7 +1905,7 @@
       </c>
       <c r="J28" s="9">
         <f>AVERAGE($E$4:E28)</f>
-        <v>9.24</v>
+        <v>15.88</v>
       </c>
       <c r="K28" s="11"/>
     </row>
@@ -1635,16 +1916,16 @@
       <c r="B29" s="13"/>
       <c r="C29" s="6"/>
       <c r="D29" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E29" s="8">
         <f t="shared" si="0"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F29" s="6"/>
       <c r="G29" s="14">
         <f>SUM($C$4:C29)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H29" s="14" t="str">
         <f t="shared" si="1"/>
@@ -1656,7 +1937,7 @@
       </c>
       <c r="J29" s="14">
         <f>AVERAGE($E$4:E29)</f>
-        <v>8.7692307692307701</v>
+        <v>15.26923076923077</v>
       </c>
       <c r="K29" s="11"/>
     </row>
@@ -1667,16 +1948,16 @@
       <c r="B30" s="13"/>
       <c r="C30" s="6"/>
       <c r="D30" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E30" s="8">
         <f t="shared" si="0"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F30" s="6"/>
       <c r="G30" s="9">
         <f>SUM($C$4:C30)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H30" s="9" t="str">
         <f t="shared" si="1"/>
@@ -1688,7 +1969,7 @@
       </c>
       <c r="J30" s="9">
         <f>AVERAGE($E$4:E30)</f>
-        <v>8.3333333333333339</v>
+        <v>14.703703703703704</v>
       </c>
       <c r="K30" s="11"/>
     </row>
@@ -1699,16 +1980,16 @@
       <c r="B31" s="13"/>
       <c r="C31" s="6"/>
       <c r="D31" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E31" s="8">
         <f t="shared" si="0"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F31" s="6"/>
       <c r="G31" s="14">
         <f>SUM($C$4:C31)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H31" s="14" t="str">
         <f t="shared" si="1"/>
@@ -1720,7 +2001,7 @@
       </c>
       <c r="J31" s="14">
         <f>AVERAGE($E$4:E31)</f>
-        <v>7.9285714285714288</v>
+        <v>14.178571428571429</v>
       </c>
       <c r="K31" s="11"/>
     </row>
@@ -1731,16 +2012,16 @@
       <c r="B32" s="13"/>
       <c r="C32" s="6"/>
       <c r="D32" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E32" s="8">
         <f t="shared" si="0"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F32" s="6"/>
       <c r="G32" s="9">
         <f>SUM($C$4:C32)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H32" s="9" t="str">
         <f t="shared" si="1"/>
@@ -1752,7 +2033,7 @@
       </c>
       <c r="J32" s="9">
         <f>AVERAGE($E$4:E32)</f>
-        <v>7.5517241379310347</v>
+        <v>13.689655172413794</v>
       </c>
       <c r="K32" s="11"/>
     </row>
@@ -1763,16 +2044,16 @@
       <c r="B33" s="13"/>
       <c r="C33" s="6"/>
       <c r="D33" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E33" s="8">
         <f t="shared" si="0"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F33" s="6"/>
       <c r="G33" s="14">
         <f>SUM($C$4:C33)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H33" s="14" t="str">
         <f t="shared" si="1"/>
@@ -1784,7 +2065,7 @@
       </c>
       <c r="J33" s="14">
         <f>AVERAGE($E$4:E33)</f>
-        <v>7.2</v>
+        <v>13.233333333333333</v>
       </c>
       <c r="K33" s="11"/>
     </row>
@@ -1795,16 +2076,16 @@
       <c r="B34" s="13"/>
       <c r="C34" s="6"/>
       <c r="D34" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E34" s="8">
         <f t="shared" si="0"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F34" s="6"/>
       <c r="G34" s="9">
         <f>SUM($C$4:C34)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H34" s="9" t="str">
         <f t="shared" si="1"/>
@@ -1816,7 +2097,7 @@
       </c>
       <c r="J34" s="9">
         <f>AVERAGE($E$4:E34)</f>
-        <v>6.870967741935484</v>
+        <v>12.806451612903226</v>
       </c>
       <c r="K34" s="11"/>
     </row>
@@ -1827,16 +2108,16 @@
       <c r="B35" s="13"/>
       <c r="C35" s="6"/>
       <c r="D35" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E35" s="8">
         <f t="shared" si="0"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F35" s="6"/>
       <c r="G35" s="14">
         <f>SUM($C$4:C35)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H35" s="14" t="str">
         <f t="shared" si="1"/>
@@ -1848,7 +2129,7 @@
       </c>
       <c r="J35" s="14">
         <f>AVERAGE($E$4:E35)</f>
-        <v>6.5625</v>
+        <v>12.40625</v>
       </c>
       <c r="K35" s="11"/>
     </row>
@@ -1859,16 +2140,16 @@
       <c r="B36" s="13"/>
       <c r="C36" s="6"/>
       <c r="D36" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E36" s="8">
         <f t="shared" ref="E36:E63" si="3">C36-D36</f>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F36" s="6"/>
       <c r="G36" s="9">
         <f>SUM($C$4:C36)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H36" s="9" t="str">
         <f t="shared" ref="H36:H63" si="4">IF(F36="","",F36-G36)</f>
@@ -1880,7 +2161,7 @@
       </c>
       <c r="J36" s="9">
         <f>AVERAGE($E$4:E36)</f>
-        <v>6.2727272727272725</v>
+        <v>12.030303030303031</v>
       </c>
       <c r="K36" s="11"/>
     </row>
@@ -1891,16 +2172,16 @@
       <c r="B37" s="13"/>
       <c r="C37" s="6"/>
       <c r="D37" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E37" s="8">
         <f t="shared" si="3"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F37" s="6"/>
       <c r="G37" s="14">
         <f>SUM($C$4:C37)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H37" s="14" t="str">
         <f t="shared" si="4"/>
@@ -1912,7 +2193,7 @@
       </c>
       <c r="J37" s="14">
         <f>AVERAGE($E$4:E37)</f>
-        <v>6</v>
+        <v>11.676470588235293</v>
       </c>
       <c r="K37" s="11"/>
     </row>
@@ -1923,16 +2204,16 @@
       <c r="B38" s="13"/>
       <c r="C38" s="6"/>
       <c r="D38" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E38" s="8">
         <f t="shared" si="3"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F38" s="6"/>
       <c r="G38" s="9">
         <f>SUM($C$4:C38)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H38" s="9" t="str">
         <f t="shared" si="4"/>
@@ -1944,7 +2225,7 @@
       </c>
       <c r="J38" s="9">
         <f>AVERAGE($E$4:E38)</f>
-        <v>5.7428571428571429</v>
+        <v>11.342857142857143</v>
       </c>
       <c r="K38" s="11"/>
     </row>
@@ -1955,16 +2236,16 @@
       <c r="B39" s="13"/>
       <c r="C39" s="6"/>
       <c r="D39" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E39" s="8">
         <f t="shared" si="3"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F39" s="6"/>
       <c r="G39" s="14">
         <f>SUM($C$4:C39)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H39" s="14" t="str">
         <f t="shared" si="4"/>
@@ -1976,7 +2257,7 @@
       </c>
       <c r="J39" s="14">
         <f>AVERAGE($E$4:E39)</f>
-        <v>5.5</v>
+        <v>11.027777777777779</v>
       </c>
       <c r="K39" s="11"/>
     </row>
@@ -1987,16 +2268,16 @@
       <c r="B40" s="13"/>
       <c r="C40" s="6"/>
       <c r="D40" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E40" s="8">
         <f t="shared" si="3"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F40" s="6"/>
       <c r="G40" s="9">
         <f>SUM($C$4:C40)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H40" s="9" t="str">
         <f t="shared" si="4"/>
@@ -2008,7 +2289,7 @@
       </c>
       <c r="J40" s="9">
         <f>AVERAGE($E$4:E40)</f>
-        <v>5.2702702702702702</v>
+        <v>10.72972972972973</v>
       </c>
       <c r="K40" s="11"/>
     </row>
@@ -2019,16 +2300,16 @@
       <c r="B41" s="13"/>
       <c r="C41" s="6"/>
       <c r="D41" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E41" s="8">
         <f t="shared" si="3"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F41" s="6"/>
       <c r="G41" s="14">
         <f>SUM($C$4:C41)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H41" s="14" t="str">
         <f t="shared" si="4"/>
@@ -2040,7 +2321,7 @@
       </c>
       <c r="J41" s="14">
         <f>AVERAGE($E$4:E41)</f>
-        <v>5.0526315789473681</v>
+        <v>10.447368421052632</v>
       </c>
       <c r="K41" s="11"/>
     </row>
@@ -2051,16 +2332,16 @@
       <c r="B42" s="13"/>
       <c r="C42" s="6"/>
       <c r="D42" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E42" s="8">
         <f t="shared" si="3"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F42" s="6"/>
       <c r="G42" s="9">
         <f>SUM($C$4:C42)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H42" s="9" t="str">
         <f t="shared" si="4"/>
@@ -2072,7 +2353,7 @@
       </c>
       <c r="J42" s="9">
         <f>AVERAGE($E$4:E42)</f>
-        <v>4.8461538461538458</v>
+        <v>10.179487179487179</v>
       </c>
       <c r="K42" s="11"/>
     </row>
@@ -2083,16 +2364,16 @@
       <c r="B43" s="13"/>
       <c r="C43" s="6"/>
       <c r="D43" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E43" s="8">
         <f t="shared" si="3"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F43" s="6"/>
       <c r="G43" s="14">
         <f>SUM($C$4:C43)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H43" s="14" t="str">
         <f t="shared" si="4"/>
@@ -2104,7 +2385,7 @@
       </c>
       <c r="J43" s="14">
         <f>AVERAGE($E$4:E43)</f>
-        <v>4.6500000000000004</v>
+        <v>9.9250000000000007</v>
       </c>
       <c r="K43" s="11"/>
     </row>
@@ -2115,16 +2396,16 @@
       <c r="B44" s="13"/>
       <c r="C44" s="6"/>
       <c r="D44" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E44" s="8">
         <f t="shared" si="3"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F44" s="6"/>
       <c r="G44" s="9">
         <f>SUM($C$4:C44)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H44" s="9" t="str">
         <f t="shared" si="4"/>
@@ -2136,7 +2417,7 @@
       </c>
       <c r="J44" s="9">
         <f>AVERAGE($E$4:E44)</f>
-        <v>4.4634146341463419</v>
+        <v>9.6829268292682933</v>
       </c>
       <c r="K44" s="11"/>
     </row>
@@ -2147,16 +2428,16 @@
       <c r="B45" s="13"/>
       <c r="C45" s="6"/>
       <c r="D45" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E45" s="8">
         <f t="shared" si="3"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F45" s="6"/>
       <c r="G45" s="14">
         <f>SUM($C$4:C45)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H45" s="14" t="str">
         <f t="shared" si="4"/>
@@ -2168,7 +2449,7 @@
       </c>
       <c r="J45" s="14">
         <f>AVERAGE($E$4:E45)</f>
-        <v>4.2857142857142856</v>
+        <v>9.4523809523809526</v>
       </c>
       <c r="K45" s="11"/>
     </row>
@@ -2179,16 +2460,16 @@
       <c r="B46" s="13"/>
       <c r="C46" s="6"/>
       <c r="D46" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E46" s="8">
         <f t="shared" si="3"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F46" s="6"/>
       <c r="G46" s="9">
         <f>SUM($C$4:C46)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H46" s="9" t="str">
         <f t="shared" si="4"/>
@@ -2200,7 +2481,7 @@
       </c>
       <c r="J46" s="9">
         <f>AVERAGE($E$4:E46)</f>
-        <v>4.1162790697674421</v>
+        <v>9.2325581395348841</v>
       </c>
       <c r="K46" s="11"/>
     </row>
@@ -2211,16 +2492,16 @@
       <c r="B47" s="13"/>
       <c r="C47" s="6"/>
       <c r="D47" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E47" s="8">
         <f t="shared" si="3"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F47" s="6"/>
       <c r="G47" s="14">
         <f>SUM($C$4:C47)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H47" s="14" t="str">
         <f t="shared" si="4"/>
@@ -2232,7 +2513,7 @@
       </c>
       <c r="J47" s="14">
         <f>AVERAGE($E$4:E47)</f>
-        <v>3.9545454545454546</v>
+        <v>9.0227272727272734</v>
       </c>
       <c r="K47" s="11"/>
     </row>
@@ -2243,16 +2524,16 @@
       <c r="B48" s="13"/>
       <c r="C48" s="6"/>
       <c r="D48" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E48" s="8">
         <f t="shared" si="3"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F48" s="6"/>
       <c r="G48" s="9">
         <f>SUM($C$4:C48)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H48" s="9" t="str">
         <f t="shared" si="4"/>
@@ -2264,7 +2545,7 @@
       </c>
       <c r="J48" s="9">
         <f>AVERAGE($E$4:E48)</f>
-        <v>3.8</v>
+        <v>8.8222222222222229</v>
       </c>
       <c r="K48" s="11"/>
     </row>
@@ -2275,16 +2556,16 @@
       <c r="B49" s="13"/>
       <c r="C49" s="6"/>
       <c r="D49" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E49" s="8">
         <f t="shared" si="3"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F49" s="6"/>
       <c r="G49" s="14">
         <f>SUM($C$4:C49)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H49" s="14" t="str">
         <f t="shared" si="4"/>
@@ -2296,7 +2577,7 @@
       </c>
       <c r="J49" s="14">
         <f>AVERAGE($E$4:E49)</f>
-        <v>3.652173913043478</v>
+        <v>8.6304347826086953</v>
       </c>
       <c r="K49" s="11"/>
     </row>
@@ -2307,16 +2588,16 @@
       <c r="B50" s="13"/>
       <c r="C50" s="6"/>
       <c r="D50" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E50" s="8">
         <f t="shared" si="3"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F50" s="6"/>
       <c r="G50" s="9">
         <f>SUM($C$4:C50)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H50" s="9" t="str">
         <f t="shared" si="4"/>
@@ -2328,7 +2609,7 @@
       </c>
       <c r="J50" s="9">
         <f>AVERAGE($E$4:E50)</f>
-        <v>3.5106382978723403</v>
+        <v>8.4468085106382986</v>
       </c>
       <c r="K50" s="11"/>
     </row>
@@ -2339,16 +2620,16 @@
       <c r="B51" s="13"/>
       <c r="C51" s="6"/>
       <c r="D51" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E51" s="8">
         <f t="shared" si="3"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F51" s="6"/>
       <c r="G51" s="14">
         <f>SUM($C$4:C51)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H51" s="14" t="str">
         <f t="shared" si="4"/>
@@ -2360,7 +2641,7 @@
       </c>
       <c r="J51" s="14">
         <f>AVERAGE($E$4:E51)</f>
-        <v>3.375</v>
+        <v>8.2708333333333339</v>
       </c>
       <c r="K51" s="11"/>
     </row>
@@ -2371,16 +2652,16 @@
       <c r="B52" s="13"/>
       <c r="C52" s="6"/>
       <c r="D52" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E52" s="8">
         <f t="shared" si="3"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F52" s="6"/>
       <c r="G52" s="9">
         <f>SUM($C$4:C52)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H52" s="9" t="str">
         <f t="shared" si="4"/>
@@ -2392,7 +2673,7 @@
       </c>
       <c r="J52" s="9">
         <f>AVERAGE($E$4:E52)</f>
-        <v>3.2448979591836733</v>
+        <v>8.1020408163265305</v>
       </c>
       <c r="K52" s="11"/>
     </row>
@@ -2403,16 +2684,16 @@
       <c r="B53" s="13"/>
       <c r="C53" s="6"/>
       <c r="D53" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E53" s="8">
         <f t="shared" si="3"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F53" s="6"/>
       <c r="G53" s="14">
         <f>SUM($C$4:C53)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H53" s="14" t="str">
         <f t="shared" si="4"/>
@@ -2424,7 +2705,7 @@
       </c>
       <c r="J53" s="14">
         <f>AVERAGE($E$4:E53)</f>
-        <v>3.12</v>
+        <v>7.94</v>
       </c>
       <c r="K53" s="11"/>
     </row>
@@ -2435,16 +2716,16 @@
       <c r="B54" s="13"/>
       <c r="C54" s="6"/>
       <c r="D54" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E54" s="8">
         <f t="shared" si="3"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F54" s="6"/>
       <c r="G54" s="9">
         <f>SUM($C$4:C54)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H54" s="9" t="str">
         <f t="shared" si="4"/>
@@ -2456,7 +2737,7 @@
       </c>
       <c r="J54" s="9">
         <f>AVERAGE($E$4:E54)</f>
-        <v>3</v>
+        <v>7.784313725490196</v>
       </c>
       <c r="K54" s="11"/>
     </row>
@@ -2467,16 +2748,16 @@
       <c r="B55" s="13"/>
       <c r="C55" s="6"/>
       <c r="D55" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E55" s="8">
         <f t="shared" si="3"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F55" s="6"/>
       <c r="G55" s="14">
         <f>SUM($C$4:C55)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H55" s="14" t="str">
         <f t="shared" si="4"/>
@@ -2488,7 +2769,7 @@
       </c>
       <c r="J55" s="14">
         <f>AVERAGE($E$4:E55)</f>
-        <v>2.8846153846153846</v>
+        <v>7.634615384615385</v>
       </c>
       <c r="K55" s="11"/>
     </row>
@@ -2499,16 +2780,16 @@
       <c r="B56" s="13"/>
       <c r="C56" s="6"/>
       <c r="D56" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E56" s="8">
         <f t="shared" si="3"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F56" s="6"/>
       <c r="G56" s="9">
         <f>SUM($C$4:C56)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H56" s="9" t="str">
         <f t="shared" si="4"/>
@@ -2520,7 +2801,7 @@
       </c>
       <c r="J56" s="9">
         <f>AVERAGE($E$4:E56)</f>
-        <v>2.7735849056603774</v>
+        <v>7.4905660377358494</v>
       </c>
       <c r="K56" s="11"/>
     </row>
@@ -2531,16 +2812,16 @@
       <c r="B57" s="13"/>
       <c r="C57" s="6"/>
       <c r="D57" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E57" s="8">
         <f t="shared" si="3"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F57" s="6"/>
       <c r="G57" s="14">
         <f>SUM($C$4:C57)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H57" s="14" t="str">
         <f t="shared" si="4"/>
@@ -2552,7 +2833,7 @@
       </c>
       <c r="J57" s="14">
         <f>AVERAGE($E$4:E57)</f>
-        <v>2.6666666666666665</v>
+        <v>7.3518518518518521</v>
       </c>
       <c r="K57" s="11"/>
     </row>
@@ -2563,16 +2844,16 @@
       <c r="B58" s="13"/>
       <c r="C58" s="6"/>
       <c r="D58" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E58" s="8">
         <f t="shared" si="3"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F58" s="6"/>
       <c r="G58" s="9">
         <f>SUM($C$4:C58)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H58" s="9" t="str">
         <f t="shared" si="4"/>
@@ -2584,7 +2865,7 @@
       </c>
       <c r="J58" s="9">
         <f>AVERAGE($E$4:E58)</f>
-        <v>2.5636363636363635</v>
+        <v>7.2181818181818178</v>
       </c>
       <c r="K58" s="11"/>
     </row>
@@ -2595,16 +2876,16 @@
       <c r="B59" s="13"/>
       <c r="C59" s="6"/>
       <c r="D59" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E59" s="8">
         <f t="shared" si="3"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F59" s="6"/>
       <c r="G59" s="14">
         <f>SUM($C$4:C59)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H59" s="14" t="str">
         <f t="shared" si="4"/>
@@ -2616,7 +2897,7 @@
       </c>
       <c r="J59" s="14">
         <f>AVERAGE($E$4:E59)</f>
-        <v>2.4642857142857144</v>
+        <v>7.0892857142857144</v>
       </c>
       <c r="K59" s="11"/>
     </row>
@@ -2627,16 +2908,16 @@
       <c r="B60" s="13"/>
       <c r="C60" s="6"/>
       <c r="D60" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E60" s="8">
         <f t="shared" si="3"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F60" s="6"/>
       <c r="G60" s="9">
         <f>SUM($C$4:C60)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H60" s="9" t="str">
         <f t="shared" si="4"/>
@@ -2648,7 +2929,7 @@
       </c>
       <c r="J60" s="9">
         <f>AVERAGE($E$4:E60)</f>
-        <v>2.3684210526315788</v>
+        <v>6.9649122807017543</v>
       </c>
       <c r="K60" s="11"/>
     </row>
@@ -2659,16 +2940,16 @@
       <c r="B61" s="13"/>
       <c r="C61" s="6"/>
       <c r="D61" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E61" s="8">
         <f t="shared" si="3"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F61" s="6"/>
       <c r="G61" s="14">
         <f>SUM($C$4:C61)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H61" s="14" t="str">
         <f t="shared" si="4"/>
@@ -2680,7 +2961,7 @@
       </c>
       <c r="J61" s="14">
         <f>AVERAGE($E$4:E61)</f>
-        <v>2.2758620689655173</v>
+        <v>6.8448275862068968</v>
       </c>
       <c r="K61" s="11"/>
     </row>
@@ -2691,16 +2972,16 @@
       <c r="B62" s="13"/>
       <c r="C62" s="6"/>
       <c r="D62" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E62" s="8">
         <f t="shared" si="3"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F62" s="6"/>
       <c r="G62" s="9">
         <f>SUM($C$4:C62)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H62" s="9" t="str">
         <f t="shared" si="4"/>
@@ -2712,7 +2993,7 @@
       </c>
       <c r="J62" s="9">
         <f>AVERAGE($E$4:E62)</f>
-        <v>2.1864406779661016</v>
+        <v>6.7288135593220337</v>
       </c>
       <c r="K62" s="11"/>
     </row>
@@ -2723,16 +3004,16 @@
       <c r="B63" s="13"/>
       <c r="C63" s="6"/>
       <c r="D63" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E63" s="8">
         <f t="shared" si="3"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F63" s="6"/>
       <c r="G63" s="14">
         <f>SUM($C$4:C63)</f>
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="H63" s="14" t="str">
         <f t="shared" si="4"/>
@@ -2744,7 +3025,7 @@
       </c>
       <c r="J63" s="14">
         <f>AVERAGE($E$4:E63)</f>
-        <v>2.1</v>
+        <v>6.6166666666666663</v>
       </c>
       <c r="K63" s="11"/>
     </row>
@@ -2771,13 +3052,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
     </row>
     <row r="2" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
@@ -2789,14 +3070,14 @@
       <c r="E2" s="25"/>
     </row>
     <row r="3" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="32"/>
-      <c r="D3" s="32" t="s">
+      <c r="B3" s="27"/>
+      <c r="D3" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="32"/>
+      <c r="E3" s="27"/>
       <c r="F3" s="16" t="s">
         <v>18</v>
       </c>
@@ -2810,12 +3091,12 @@
       </c>
       <c r="B4" s="18">
         <f>IFERROR(LOOKUP(2,1/(Registro_Mensual!G4:G63&lt;&gt;""),Registro_Mensual!G4:G63),"")</f>
-        <v>306</v>
-      </c>
-      <c r="D4" s="33" t="s">
+        <v>406</v>
+      </c>
+      <c r="D4" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="33"/>
+      <c r="E4" s="28"/>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
@@ -2823,14 +3104,14 @@
       </c>
       <c r="B5" s="18">
         <f ca="1">OFFSET(Registro_Mensual!F3,COUNTA(Registro_Mensual!F4:F63),0)</f>
-        <v>319</v>
+        <v>420</v>
       </c>
       <c r="D5" s="17" t="s">
         <v>23</v>
       </c>
       <c r="E5" s="18">
         <f>B8</f>
-        <v>99</v>
+        <v>99.25</v>
       </c>
       <c r="F5" s="19"/>
       <c r="G5" s="19"/>
@@ -2841,7 +3122,7 @@
       </c>
       <c r="B6" s="18">
         <f ca="1">IFERROR(B5-B4,"")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>25</v>
@@ -2858,22 +3139,22 @@
       </c>
       <c r="B7" s="21">
         <f ca="1">IFERROR(B5/B4-1,"")</f>
-        <v>4.2483660130719025E-2</v>
+        <v>3.4482758620689724E-2</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>27</v>
       </c>
       <c r="E7" s="18">
         <f>E5*((1+E6/12)^60-1)/(E6/12)</f>
-        <v>7274.2087682788506</v>
+        <v>7292.5779823401608</v>
       </c>
       <c r="F7" s="23">
         <f>E5*60</f>
-        <v>5940</v>
+        <v>5955</v>
       </c>
       <c r="G7" s="23">
         <f>E7-F7</f>
-        <v>1334.2087682788506</v>
+        <v>1337.5779823401608</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2882,22 +3163,22 @@
       </c>
       <c r="B8" s="18">
         <f>IFERROR(AVERAGEIF(Registro_Mensual!C4:C63,"&gt;0",Registro_Mensual!E4:E63),"")</f>
-        <v>99</v>
+        <v>99.25</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>29</v>
       </c>
       <c r="E8" s="18">
         <f>E5*((1+E6/12)^120-1)/(E6/12)</f>
-        <v>18111.657482989005</v>
+        <v>18157.393991784433</v>
       </c>
       <c r="F8" s="23">
         <f>E5*120</f>
-        <v>11880</v>
+        <v>11910</v>
       </c>
       <c r="G8" s="23">
         <f>E8-F8</f>
-        <v>6231.6574829890051</v>
+        <v>6247.3939917844327</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2906,43 +3187,43 @@
       </c>
       <c r="B9" s="22">
         <f>COUNTIF(Registro_Mensual!C4:C63,"&gt;0")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" s="17" t="s">
         <v>31</v>
       </c>
       <c r="E9" s="18">
         <f>E5*((1+E6/12)^240-1)/(E6/12)</f>
-        <v>58313.021146524254</v>
+        <v>58460.276250429619</v>
       </c>
       <c r="F9" s="23">
         <f>E5*240</f>
-        <v>23760</v>
+        <v>23820</v>
       </c>
       <c r="G9" s="23">
         <f>E9-F9</f>
-        <v>34553.021146524254</v>
+        <v>34640.276250429619</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="28" t="s">
+      <c r="A10" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="28"/>
+      <c r="B10" s="31"/>
       <c r="D10" s="17" t="s">
         <v>33</v>
       </c>
       <c r="E10" s="18">
         <f>E5*((1+E6/12)^360-1)/(E6/12)</f>
-        <v>147545.58541767095</v>
+        <v>147918.17527983681</v>
       </c>
       <c r="F10" s="23">
         <f>E5*360</f>
-        <v>35640</v>
+        <v>35730</v>
       </c>
       <c r="G10" s="23">
         <f>E10-F10</f>
-        <v>111905.58541767095</v>
+        <v>112188.17527983681</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2953,84 +3234,79 @@
       </c>
       <c r="E11" s="18">
         <f>E5*((1+E6/12)^480-1)/(E6/12)</f>
-        <v>345609.77530550543</v>
+        <v>346482.52726334758</v>
       </c>
       <c r="F11" s="23">
         <f>E5*480</f>
-        <v>47520</v>
+        <v>47640</v>
       </c>
       <c r="G11" s="23">
         <f>E11-F11</f>
-        <v>298089.77530550543</v>
+        <v>298842.52726334758</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D12" s="29" t="s">
+      <c r="D12" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="E12" s="29"/>
+      <c r="E12" s="32"/>
     </row>
     <row r="13" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="30" t="s">
+      <c r="A13" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="30"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
     </row>
     <row r="14" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="26" t="s">
+      <c r="A14" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="26"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26"/>
+      <c r="B14" s="29"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
     </row>
     <row r="15" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="27" t="s">
+      <c r="A15" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="27"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="27"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="30"/>
     </row>
     <row r="16" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="26" t="s">
+      <c r="A16" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="26"/>
-      <c r="C16" s="26"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="26"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
     </row>
     <row r="17" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="27"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="27"/>
+      <c r="B17" s="30"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="30"/>
     </row>
     <row r="18" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="26" t="s">
+      <c r="A18" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="26"/>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26"/>
+      <c r="B18" s="29"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A18:E18"/>
@@ -3039,8 +3315,273 @@
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6C2CF63-A9CC-4BE2-B119-A050F91FC767}">
+  <dimension ref="B1:G12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" style="35" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" style="44"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B1" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" s="45"/>
+      <c r="E1" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+    </row>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G2" s="44" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="38">
+        <v>132</v>
+      </c>
+      <c r="E3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F3" s="34">
+        <v>46218</v>
+      </c>
+      <c r="G3" s="44">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="38">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4" s="34">
+        <v>46219</v>
+      </c>
+      <c r="G4" s="44">
+        <v>7.88</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="38">
+        <v>32</v>
+      </c>
+      <c r="E5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" s="34">
+        <v>46220</v>
+      </c>
+      <c r="G5" s="44">
+        <v>19.399999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="37"/>
+      <c r="C6" s="38"/>
+      <c r="E6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="34">
+        <v>46232</v>
+      </c>
+      <c r="G6" s="44">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="37"/>
+      <c r="C7" s="38"/>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="37"/>
+      <c r="C8" s="38"/>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="37"/>
+      <c r="C9" s="38"/>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="37"/>
+      <c r="C10" s="38"/>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="39"/>
+      <c r="C11" s="40"/>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="36">
+        <f>SUM(C3:C11)</f>
+        <v>184</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C3">
+    <cfRule type="dataBar" priority="4">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{E26128B9-01F4-46FC-8E97-42D3D183D502}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C3:C11 C13:C1048576">
+    <cfRule type="dataBar" priority="3">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{77F84ACE-D316-480D-B918-04CEA84DBCE9}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2">
+    <cfRule type="dataBar" priority="2">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{8574F4BE-9390-4DEC-A36D-A8EC7E2D95CF}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{A19D6E6F-6841-43C9-8235-0F835BE2EFF0}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="2">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+  </tableParts>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{E26128B9-01F4-46FC-8E97-42D3D183D502}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF63C384"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>C3</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{77F84ACE-D316-480D-B918-04CEA84DBCE9}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF63C384"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>C3:C11 C13:C1048576</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{8574F4BE-9390-4DEC-A36D-A8EC7E2D95CF}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF63C384"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>C2</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{A19D6E6F-6841-43C9-8235-0F835BE2EFF0}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF63C384"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>C2</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
+</worksheet>
 </file>
--- a/inversiones.xlsx
+++ b/inversiones.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marag\Documents\GitHub\inversiones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A8F11B1-AA28-48F6-AE24-7A44738EBC4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{027EB88B-3810-4F20-9235-9DB7343E9416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro_Mensual" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="54">
   <si>
     <t>📈 SEGUIMIENTO DE INVERSIONES — S&amp;P 500</t>
   </si>
@@ -202,6 +202,15 @@
   </si>
   <si>
     <t>Balance 2026</t>
+  </si>
+  <si>
+    <t>IRPF (19%)</t>
+  </si>
+  <si>
+    <t>2026 NETO</t>
+  </si>
+  <si>
+    <t>Acumulado</t>
   </si>
 </sst>
 </file>
@@ -325,7 +334,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -398,8 +407,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF7C80"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -432,21 +453,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFBDC3C7"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -525,7 +531,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -622,26 +628,33 @@
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="173" fontId="0" fillId="11" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="173" fontId="0" fillId="13" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="173" fontId="0" fillId="14" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="0" fillId="11" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="8">
+    <dxf>
+      <numFmt numFmtId="174" formatCode="_-* #,##0.00\ [$€-C0A]_-;\-* #,##0.00\ [$€-C0A]_-;_-* &quot;-&quot;??\ [$€-C0A]_-;_-@_-"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="174" formatCode="_-* #,##0.00\ [$€-C0A]_-;\-* #,##0.00\ [$€-C0A]_-;_-* &quot;-&quot;??\ [$€-C0A]_-;_-@_-"/>
     </dxf>
@@ -797,6 +810,10 @@
       <rgbColor rgb="00333399"/>
       <rgbColor rgb="00333333"/>
     </indexedColors>
+    <mruColors>
+      <color rgb="FFFF7C80"/>
+      <color rgb="FFFF5050"/>
+    </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -809,24 +826,1093 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mj-lt"/>
+                <a:ea typeface="+mj-ea"/>
+                <a:cs typeface="+mj-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-ES"/>
+              <a:t>Evolución 2026</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mj-lt"/>
+              <a:ea typeface="+mj-ea"/>
+              <a:cs typeface="+mj-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Beneficios bolsa'!$G$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v> Balance </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'Beneficios bolsa'!$E$3:$F$6</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="4"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>15-jul</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>16-jul</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>17-jul</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>29-jul</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>SP500</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>SP500</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Allianz</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Coca Cola</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Beneficios bolsa'!$G$3:$G$6</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0.00\ [$€-C0A]_-;\-* #,##0.00\ [$€-C0A]_-;_-* "-"??\ [$€-C0A]_-;_-@_-</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.88</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>19.399999999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>131</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D44D-4840-9C32-79F50EB9C685}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="269"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1885366847"/>
+        <c:axId val="1885367263"/>
+      </c:barChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Beneficios bolsa'!$H$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Acumulado</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'Beneficios bolsa'!$E$3:$F$6</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="4"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>15-jul</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>16-jul</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>17-jul</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>29-jul</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>SP500</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>SP500</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Allianz</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Coca Cola</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Beneficios bolsa'!$H$3:$H$6</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0.00\ [$€-C0A]_-;\-* #,##0.00\ [$€-C0A]_-;_-* "-"??\ [$€-C0A]_-;_-@_-</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15.879999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>35.28</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>166.28</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-D44D-4840-9C32-79F50EB9C685}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1885366847"/>
+        <c:axId val="1885367263"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1885366847"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1885367263"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1885367263"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:numFmt formatCode="_-* #,##0.00\ [$€-C0A]_-;\-* #,##0.00\ [$€-C0A]_-;_-* &quot;-&quot;??\ [$€-C0A]_-;_-@_-" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1885366847"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="50"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-ES"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="225">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" b="0" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="38100" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="8"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="major">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="2000" b="0" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>71437</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>147637</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CAC9278C-46FA-408B-A02E-0D893F00D890}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{43361EA0-38CE-405F-999E-E678479A76FE}" name="Tabla3" displayName="Tabla3" ref="B2:C11" totalsRowShown="0" headerRowBorderDxfId="5" tableBorderDxfId="6" totalsRowBorderDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{43361EA0-38CE-405F-999E-E678479A76FE}" name="Tabla3" displayName="Tabla3" ref="B2:C11" totalsRowShown="0" headerRowBorderDxfId="6" tableBorderDxfId="7" totalsRowBorderDxfId="5">
   <autoFilter ref="B2:C11" xr:uid="{43361EA0-38CE-405F-999E-E678479A76FE}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:C11">
+    <sortCondition descending="1" ref="C3:C11"/>
+  </sortState>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{5452176F-36B8-4CDD-9F33-5D70AA66A550}" name="Mercado" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{AA88D4F0-70F9-4823-81E5-D366BE0621A3}" name="Balance" dataDxfId="2" dataCellStyle="Moneda"/>
+    <tableColumn id="1" xr3:uid="{5452176F-36B8-4CDD-9F33-5D70AA66A550}" name="Mercado" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{AA88D4F0-70F9-4823-81E5-D366BE0621A3}" name="Balance" dataDxfId="3" dataCellStyle="Moneda">
+      <calculatedColumnFormula>SUMIF(E:E,B3,G:G)</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E0EF1798-5DBC-4CC2-BF2B-D1627830BBD8}" name="Tabla4" displayName="Tabla4" ref="E2:G6" totalsRowShown="0">
-  <autoFilter ref="E2:G6" xr:uid="{E0EF1798-5DBC-4CC2-BF2B-D1627830BBD8}"/>
-  <tableColumns count="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E0EF1798-5DBC-4CC2-BF2B-D1627830BBD8}" name="Tabla4" displayName="Tabla4" ref="E2:H6" totalsRowShown="0">
+  <autoFilter ref="E2:H6" xr:uid="{E0EF1798-5DBC-4CC2-BF2B-D1627830BBD8}"/>
+  <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{D7244F53-013B-49D1-84D7-0E66C32F39B4}" name="Mercado"/>
-    <tableColumn id="2" xr3:uid="{28786B65-FA4E-4DA6-9569-A775903889EB}" name="Fecha venta" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{00894C4B-3E6A-4755-9F14-59B8AD97246A}" name="Balance" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{28786B65-FA4E-4DA6-9569-A775903889EB}" name="Fecha venta" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{00894C4B-3E6A-4755-9F14-59B8AD97246A}" name="Balance" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{2A5F1324-D18F-4866-A09B-AC0F8A8E977C}" name="Acumulado" dataDxfId="0">
+      <calculatedColumnFormula>SUM($G$3:G3)</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3328,32 +4414,33 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6C2CF63-A9CC-4BE2-B119-A050F91FC767}">
-  <dimension ref="B1:G12"/>
+  <dimension ref="B1:H14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="13.42578125" style="35" customWidth="1"/>
     <col min="5" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.7109375" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" style="44"/>
+    <col min="7" max="7" width="11.42578125" style="42"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B1" s="45" t="s">
+    <row r="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="45"/>
-      <c r="E1" s="45" t="s">
+      <c r="C1" s="43"/>
+      <c r="E1" s="43" t="s">
         <v>47</v>
       </c>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-    </row>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="41" t="s">
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+    </row>
+    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B2" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="43" t="s">
+      <c r="C2" s="41" t="s">
         <v>48</v>
       </c>
       <c r="E2" t="s">
@@ -3362,16 +4449,20 @@
       <c r="F2" t="s">
         <v>49</v>
       </c>
-      <c r="G2" s="44" t="s">
+      <c r="G2" s="42" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="37" t="s">
+      <c r="H2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B3" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="38">
-        <v>132</v>
+      <c r="C3" s="37">
+        <f>SUMIF(E:E,B3,G:G)</f>
+        <v>131</v>
       </c>
       <c r="E3" t="s">
         <v>45</v>
@@ -3379,16 +4470,21 @@
       <c r="F3" s="34">
         <v>46218</v>
       </c>
-      <c r="G3" s="44">
+      <c r="G3" s="42">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="37" t="s">
+      <c r="H3" s="42">
+        <f>SUM($G$3:G3)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B4" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="38">
-        <v>20</v>
+      <c r="C4" s="37">
+        <f>SUMIF(E:E,B4,G:G)</f>
+        <v>19.399999999999999</v>
       </c>
       <c r="E4" t="s">
         <v>45</v>
@@ -3396,16 +4492,21 @@
       <c r="F4" s="34">
         <v>46219</v>
       </c>
-      <c r="G4" s="44">
+      <c r="G4" s="42">
         <v>7.88</v>
       </c>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="37" t="s">
+      <c r="H4" s="42">
+        <f>SUM($G$3:G4)</f>
+        <v>15.879999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B5" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="38">
-        <v>32</v>
+      <c r="C5" s="37">
+        <f>SUMIF(E:E,B5,G:G)</f>
+        <v>15.879999999999999</v>
       </c>
       <c r="E5" t="s">
         <v>44</v>
@@ -3413,58 +4514,102 @@
       <c r="F5" s="34">
         <v>46220</v>
       </c>
-      <c r="G5" s="44">
+      <c r="G5" s="42">
         <v>19.399999999999999</v>
       </c>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="37"/>
-      <c r="C6" s="38"/>
+      <c r="H5" s="42">
+        <f>SUM($G$3:G5)</f>
+        <v>35.28</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B6" s="36"/>
+      <c r="C6" s="37">
+        <f>SUMIF(E:E,B6,G:G)</f>
+        <v>0</v>
+      </c>
       <c r="E6" t="s">
         <v>42</v>
       </c>
       <c r="F6" s="34">
         <v>46232</v>
       </c>
-      <c r="G6" s="44">
+      <c r="G6" s="42">
         <v>131</v>
       </c>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="37"/>
-      <c r="C7" s="38"/>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="37"/>
-      <c r="C8" s="38"/>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="37"/>
-      <c r="C9" s="38"/>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="37"/>
-      <c r="C10" s="38"/>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="39"/>
-      <c r="C11" s="40"/>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="42" t="s">
+      <c r="H6" s="42">
+        <f>SUM($G$3:G6)</f>
+        <v>166.28</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B7" s="36"/>
+      <c r="C7" s="37">
+        <f>SUMIF(E:E,B7,G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B8" s="36"/>
+      <c r="C8" s="37">
+        <f>SUMIF(E:E,B8,G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B9" s="36"/>
+      <c r="C9" s="37">
+        <f>SUMIF(E:E,B9,G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B10" s="36"/>
+      <c r="C10" s="37">
+        <f>SUMIF(E:E,B10,G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B11" s="38"/>
+      <c r="C11" s="39">
+        <f>SUMIF(E:E,B11,G:G)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B12" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="36">
+      <c r="C12" s="49">
         <f>SUM(C3:C11)</f>
-        <v>184</v>
+        <v>166.28</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B13" s="45" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="44">
+        <f>C12*0.19*-1</f>
+        <v>-31.5932</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B14" s="46" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="47">
+        <f>C12+C13</f>
+        <v>134.68680000000001</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="E1:G1"/>
     <mergeCell ref="B1:C1"/>
+    <mergeCell ref="E1:H1"/>
   </mergeCells>
-  <conditionalFormatting sqref="C3">
+  <conditionalFormatting sqref="C3:C11">
     <cfRule type="dataBar" priority="4">
       <dataBar>
         <cfvo type="min"/>
@@ -3478,7 +4623,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C3:C11 C13:C1048576">
+  <conditionalFormatting sqref="C15:C1048576 C3:C11">
     <cfRule type="dataBar" priority="3">
       <dataBar>
         <cfvo type="min"/>
@@ -3521,9 +4666,10 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
   <tableParts count="2">
-    <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -3539,7 +4685,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>C3</xm:sqref>
+          <xm:sqref>C3:C11</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{77F84ACE-D316-480D-B918-04CEA84DBCE9}">
@@ -3552,7 +4698,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>C3:C11 C13:C1048576</xm:sqref>
+          <xm:sqref>C15:C1048576 C3:C11</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{8574F4BE-9390-4DEC-A36D-A8EC7E2D95CF}">
